--- a/AAII_Financials/Yearly/PRTH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PRTH_YR_FIN.xlsx
@@ -3899,7 +3899,7 @@
         <v>2100</v>
       </c>
       <c r="F83" s="3">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="G83" s="3">
         <v>2600</v>
